--- a/packages/core/test/fixtures/sample.xlsx
+++ b/packages/core/test/fixtures/sample.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,10 +483,21 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B5">
+        <f>SUM(B2:B4)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
           <t>Reported</t>
         </is>
       </c>
-      <c r="B5" s="2" t="n">
+      <c r="B6" s="2" t="n">
         <v>46288</v>
       </c>
     </row>
